--- a/outputs/supplier_passport.xlsx
+++ b/outputs/supplier_passport.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,7 +528,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>указано не во всех прайсах: FOB (прайсов: 4); EXW (прайсов: 1)</t>
+          <t>EXW</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>уточнить</t>
+          <t>EXW</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>уточнить</t>
+          <t>EXW</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>уточнить</t>
+          <t>EXW</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -782,7 +782,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KR_vt</t>
+          <t>KR_annecy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -797,63 +797,63 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>Аннеси (Annecy)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>бренд</t>
+          <t>посредник</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>annecy.kr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>EXW</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>указано не во всех прайсах: 10000000 KRW (прайсов: 1)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>189</v>
+        <v>430</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>прямой прайс бренда; позиций: 189</t>
+          <t>по CELIMAX в шапке прайса указано, что запрещенных к экспорту стран нет; у LAMELIN две цены по объему заказа — уточнить пороги</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KR_skin1004</t>
+          <t>KR_vt</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SKIN1004</t>
+          <t>VT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FOB (прайсов: 1)</t>
+          <t>EXW</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -910,21 +910,21 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c r="N7" t="n">
         <v>1</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>прямой прайс бренда; позиций: 141</t>
+          <t>прямой прайс бренда; позиций: 189</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KR_roundlab</t>
+          <t>KR_skin1004</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ROUNDLAB</t>
+          <t>SKIN1004</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -954,48 +954,48 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>EXW</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
       <c r="L8" t="n">
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>прямой прайс бренда; позиций: 100</t>
+          <t>прямой прайс бренда; позиций: 141</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KR_masil</t>
+          <t>KR_roundlab</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MASIL</t>
+          <t>ROUNDLAB</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1025,48 +1025,48 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>EXW</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>прямой прайс бренда; позиций: 93</t>
+          <t>прямой прайс бренда; позиций: 100</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KR_dermafactory</t>
+          <t>KR_papacosmetic</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1081,63 +1081,63 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DERMAFACTORY</t>
+          <t>Papacosmetic Co., Ltd</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>бренд</t>
+          <t>экспортер</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>г. Кимпхо</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>EXW</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>прямой прайс бренда; позиций: 85</t>
+          <t>минимальный заказ 100 000 000 KRW; оплата 50% + 50%; прайс CELIMAX содержит два листа с одинаковым набором товаров и ценами, отличающимися на 2.5% — взят более дорогой лист</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KR_anua</t>
+          <t>KR_masil</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ANUA</t>
+          <t>MASIL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1167,48 +1167,48 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>EXW</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
       <c r="L11" t="n">
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>прямой прайс бренда; позиций: 84</t>
+          <t>прямой прайс бренда; позиций: 93</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KR_celimax</t>
+          <t>KR_dermafactory</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CELIMAX</t>
+          <t>DERMAFACTORY</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>FOB (прайсов: 1)</t>
+          <t>EXW</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1265,21 +1265,21 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>прямой прайс бренда; позиций: 73</t>
+          <t>прямой прайс бренда; позиций: 85</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KR_dralthea</t>
+          <t>KR_anua</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DR ALTHEA</t>
+          <t>ANUA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>FOB (прайсов: 1)</t>
+          <t>EXW</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1336,83 +1336,225 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>прямой прайс бренда; позиций: 50</t>
+          <t>прямой прайс бренда; позиций: 84</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>KR_celimax</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>бренд</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>EXW</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>73</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>прямой прайс бренда; позиций: 73</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KR_dralthea</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DR ALTHEA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>бренд</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>EXW</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>50</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>прямой прайс бренда; позиций: 50</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>KR_axisy</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>AXISY</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>бренд</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>EXW</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
         <v>34</v>
       </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>прямой прайс бренда; позиций: 34</t>
         </is>
@@ -1429,7 +1571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1487,12 +1629,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ANUA_PRICE_LIST_VAT_26.04.xlsx</t>
+          <t>annecy_260626_MEDIPEEL_LIST.xlsx</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KR_anua</t>
+          <t>KR_annecy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1500,11 +1642,7 @@
           <t>KR</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>KRW</t>
@@ -1516,7 +1654,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>84</v>
+        <v>199</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1533,12 +1671,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AXISY_PRICE_LIST_VAT_26.01.xlsx</t>
+          <t>annecy_260714_CELIMAX_LIST.xlsx</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KR_axisy</t>
+          <t>KR_annecy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1546,11 +1684,7 @@
           <t>KR</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>KRW</t>
@@ -1562,7 +1696,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1579,12 +1713,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CELIMAX_PRICE_LIST_VAT_26.03.xlsx</t>
+          <t>annecy_260810_LAMELIN_LIST.xlsx</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KR_celimax</t>
+          <t>KR_annecy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1592,11 +1726,7 @@
           <t>KR</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>KRW</t>
@@ -1608,7 +1738,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1625,12 +1755,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>classic_Rataplan_Price_listVAT_24.08S.xlsx</t>
+          <t>ANUA_PRICE_LIST_VAT_26.04.xlsx</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KR_classic</t>
+          <t>KR_anua</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1640,7 +1770,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1654,7 +1784,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1671,12 +1801,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>classic_PYUNKANG_YUL_PRICE_LISTVAT_25.05.xlsx</t>
+          <t>AXISY_PRICE_LIST_VAT_26.01.xlsx</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KR_classic</t>
+          <t>KR_axisy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1686,7 +1816,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1700,7 +1830,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>121</v>
+        <v>34</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1717,12 +1847,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>classic_NAEXY_PRICE_LIST_25.08SVAT.xlsx</t>
+          <t>CELIMAX_PRICE_LIST_VAT_26.03.xlsx</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KR_classic</t>
+          <t>KR_celimax</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1732,7 +1862,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1746,7 +1876,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1763,7 +1893,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>classic_BIODANCE_PRICE_LISTVAT_25.09.xlsx</t>
+          <t>classic_Rataplan_Price_listVAT_24.08S.xlsx</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1778,7 +1908,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1792,7 +1922,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1809,7 +1939,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>classic_AMORE_PACIFIC_PRICE_LISTVAT_25.10.xlsx</t>
+          <t>classic_PYUNKANG_YUL_PRICE_LISTVAT_25.05.xlsx</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1824,7 +1954,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1838,7 +1968,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1855,7 +1985,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>classic_HEIMISH_PRICE_LIST_2025.10VAT.xlsx</t>
+          <t>classic_NAEXY_PRICE_LIST_25.08SVAT.xlsx</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1870,7 +2000,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1884,7 +2014,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1901,7 +2031,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>classic_WELCOS_PRICE_LISTVAT_25.10.xlsx</t>
+          <t>classic_BIODANCE_PRICE_LISTVAT_25.09.xlsx</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1916,7 +2046,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1930,7 +2060,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1947,7 +2077,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>classic_Im_Sorry_for_My_Skin_PRICE_LIST_25.12VAT.xlsx</t>
+          <t>classic_AMORE_PACIFIC_PRICE_LISTVAT_25.10.xlsx</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1962,7 +2092,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1976,7 +2106,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1993,7 +2123,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>classic_SOME_BY_MI_PRICE_LISTVAT_25.12S.xlsx</t>
+          <t>classic_HEIMISH_PRICE_LIST_2025.10VAT.xlsx</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2008,7 +2138,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2022,7 +2152,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -2039,7 +2169,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>classic_JUMISO_PRICE_LISTVAT_26.01.xlsx</t>
+          <t>classic_WELCOS_PRICE_LISTVAT_25.10.xlsx</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2054,7 +2184,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2068,7 +2198,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2085,7 +2215,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>classic_PETITFEE_Price_List_26.02S.xlsx</t>
+          <t>classic_Im_Sorry_for_My_Skin_PRICE_LIST_25.12VAT.xlsx</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2100,7 +2230,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2114,7 +2244,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2131,7 +2261,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>classic_ANOTHERFACE_PRICE_LISTVAT_26.03.xlsx</t>
+          <t>classic_SOME_BY_MI_PRICE_LISTVAT_25.12S.xlsx</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2146,7 +2276,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2160,7 +2290,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2177,7 +2307,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>classic_IM_FROM_PRICE_LISTVAT_26.03.xlsx</t>
+          <t>classic_JUMISO_PRICE_LISTVAT_26.01.xlsx</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2192,7 +2322,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2206,7 +2336,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2223,7 +2353,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>classic_ABIB_PRICE_LISTVAT_26.04.xlsx</t>
+          <t>classic_PETITFEE_Price_List_26.02S.xlsx</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2238,7 +2368,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2252,7 +2382,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2269,7 +2399,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>classic_BEAUTY_OF_JOSEON_PRICE_LIST_26.04VAT.xlsx</t>
+          <t>classic_ANOTHERFACE_PRICE_LISTVAT_26.03.xlsx</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2284,7 +2414,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2298,7 +2428,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2315,7 +2445,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>classic_CP1_PRICE_LISTVAT_26.04.xlsx</t>
+          <t>classic_IM_FROM_PRICE_LISTVAT_26.03.xlsx</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2330,7 +2460,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2344,7 +2474,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2361,7 +2491,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>classic_dasique_Price_ListVAT_26.04.xlsx</t>
+          <t>classic_ABIB_PRICE_LISTVAT_26.04.xlsx</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2390,7 +2520,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>161</v>
+        <v>92</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2407,7 +2537,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>classic_BEPLAIN_PRICE_LISTVAT_26.05.xlsx</t>
+          <t>classic_BEAUTY_OF_JOSEON_PRICE_LIST_26.04VAT.xlsx</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2422,7 +2552,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2436,7 +2566,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2453,7 +2583,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>classic_EKEL_PRICE_LEST_26.05VAT.xlsx</t>
+          <t>classic_CP1_PRICE_LISTVAT_26.04.xlsx</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2468,7 +2598,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2482,7 +2612,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>152</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2499,7 +2629,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>classic_LAGOM_PRICE_LISTVAT_26.05.xlsx</t>
+          <t>classic_dasique_Price_ListVAT_26.04.xlsx</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2514,7 +2644,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2528,7 +2658,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>64</v>
+        <v>161</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2545,7 +2675,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>classic_MANYO_PRICE_LISTVAT_26.05.xlsx</t>
+          <t>classic_BEPLAIN_PRICE_LISTVAT_26.05.xlsx</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2574,7 +2704,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2591,7 +2721,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>classic_MEDIPEEL_PRICE_LISTVAT_26.05.xlsx</t>
+          <t>classic_EKEL_PRICE_LEST_26.05VAT.xlsx</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2620,7 +2750,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2637,7 +2767,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>classic_APIEU_PRICE_LIST_26.06VAT.xlsx</t>
+          <t>classic_LAGOM_PRICE_LISTVAT_26.05.xlsx</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2652,7 +2782,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2666,7 +2796,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>177</v>
+        <v>64</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2683,7 +2813,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>classic_BY_WISHTREND_PRICE_LISTVAT_26.06.xlsx</t>
+          <t>classic_MANYO_PRICE_LISTVAT_26.05.xlsx</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2698,7 +2828,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2712,7 +2842,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2729,7 +2859,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>classic_Centellian_24_Madeca_PRICE_LISTVAT_26.06.xlsx</t>
+          <t>classic_MEDIPEEL_PRICE_LISTVAT_26.05.xlsx</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2744,7 +2874,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2758,7 +2888,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>51</v>
+        <v>188</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2775,7 +2905,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>classic_DR._ALTHEA_PRICE_LISTVAT_26.06_2nd.xlsx</t>
+          <t>classic_APIEU_PRICE_LIST_26.06VAT.xlsx</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2804,7 +2934,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>55</v>
+        <v>177</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2821,7 +2951,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>classic_FLOR_DE_MAN_PRICE_LISTVAT_26.06.xlsx</t>
+          <t>classic_BY_WISHTREND_PRICE_LISTVAT_26.06.xlsx</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2850,7 +2980,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2867,7 +2997,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>classic_JIGOTT_PRICE_LIST_2026.06VAT.xlsx</t>
+          <t>classic_Centellian_24_Madeca_PRICE_LISTVAT_26.06.xlsx</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2896,7 +3026,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>213</v>
+        <v>51</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2913,7 +3043,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>classic_LEBELAGE_PRICE_LIST_2026.06VAT.xlsx</t>
+          <t>classic_DR._ALTHEA_PRICE_LISTVAT_26.06_2nd.xlsx</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2942,7 +3072,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>334</v>
+        <v>55</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2959,7 +3089,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>classic_MELASMAX_PRICE_LISTVAT_26.06.xlsx</t>
+          <t>classic_FLOR_DE_MAN_PRICE_LISTVAT_26.06.xlsx</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2988,7 +3118,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -3005,7 +3135,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>classic_MISSHA_Price_List_26.06VAT.xlsx</t>
+          <t>classic_JIGOTT_PRICE_LIST_2026.06VAT.xlsx</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3034,7 +3164,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>472</v>
+        <v>213</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -3051,7 +3181,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>classic_NINELESS_PRICELIST_26.06VAT.xlsx</t>
+          <t>classic_LEBELAGE_PRICE_LIST_2026.06VAT.xlsx</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3080,7 +3210,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>34</v>
+        <v>334</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -3097,7 +3227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>classic_PRORANCE_PRICE_LIST_VAT_26.06.xlsx</t>
+          <t>classic_MELASMAX_PRICE_LISTVAT_26.06.xlsx</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3126,7 +3256,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>137</v>
+        <v>26</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -3143,7 +3273,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>classic_STARLIKE_Price_List_26.06_KRW.xlsx</t>
+          <t>classic_MISSHA_Price_List_26.06VAT.xlsx</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3172,7 +3302,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>17</v>
+        <v>472</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -3189,7 +3319,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>classic_3W_CLINIC_PRICE_LIST_2026.07S_VAT.xlsx</t>
+          <t>classic_NINELESS_PRICELIST_26.06VAT.xlsx</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3204,7 +3334,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3218,7 +3348,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>248</v>
+        <v>34</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3235,7 +3365,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>classic_C2Y_PRICE_LISTVAT_26.07.xlsx</t>
+          <t>classic_PRORANCE_PRICE_LIST_VAT_26.06.xlsx</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3250,7 +3380,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3264,7 +3394,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -3281,7 +3411,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>classic_CHARDE_PRICE_LISTVAT_26.07.xlsx</t>
+          <t>classic_STARLIKE_Price_List_26.06_KRW.xlsx</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3296,7 +3426,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3327,7 +3457,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>classic_EIOM_PRICE_LISTVAT_26.07.xlsx</t>
+          <t>classic_3W_CLINIC_PRICE_LIST_2026.07S_VAT.xlsx</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3356,7 +3486,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>13</v>
+        <v>248</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -3373,7 +3503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>classic_EVAS_PRICE_LISTVAT_26.07.xlsx</t>
+          <t>classic_C2Y_PRICE_LISTVAT_26.07.xlsx</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3402,7 +3532,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>255</v>
+        <v>52</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -3419,7 +3549,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>classic_Eshumi_Price_ListVAT_26.07.xlsx</t>
+          <t>classic_CHARDE_PRICE_LISTVAT_26.07.xlsx</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3448,7 +3578,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3465,7 +3595,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>classic_LUNARIS_PRICE_LISTVAT_26.07.xlsx</t>
+          <t>classic_EIOM_PRICE_LISTVAT_26.07.xlsx</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3494,7 +3624,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3511,7 +3641,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>classic_NeoPharm_PRICE_LISTVAT_26.07.xlsx</t>
+          <t>classic_EVAS_PRICE_LISTVAT_26.07.xlsx</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3540,7 +3670,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3557,7 +3687,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>classic_SKIN_APPLE_PRICE_LISTVAT_26.07S_2nd.xlsx</t>
+          <t>classic_Eshumi_Price_ListVAT_26.07.xlsx</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3586,7 +3716,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>342</v>
+        <v>67</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3603,7 +3733,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>classic_TENZERO_PRICE_LIST_26.07VAT.xlsx</t>
+          <t>classic_LUNARIS_PRICE_LISTVAT_26.07.xlsx</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3632,7 +3762,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>304</v>
+        <v>61</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3649,7 +3779,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>classic_WATI_FOR_SKIN_PRICE_LISTVAT_26.07.xlsx</t>
+          <t>classic_NeoPharm_PRICE_LISTVAT_26.07.xlsx</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3678,7 +3808,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>128</v>
+        <v>195</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3695,7 +3825,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>classic_ARENCIA_PRICE_LIST_VAT_26.08.xlsx</t>
+          <t>classic_SKIN_APPLE_PRICE_LISTVAT_26.07S_2nd.xlsx</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3710,7 +3840,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3724,7 +3854,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>42</v>
+        <v>342</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3741,7 +3871,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>classic_DAENG_GI_MEO_RI_PRICE_LISTVAT_26.08.xlsx</t>
+          <t>classic_TENZERO_PRICE_LIST_26.07VAT.xlsx</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3756,7 +3886,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3770,7 +3900,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>73</v>
+        <v>304</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3787,7 +3917,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>classic_DAYCELLDr.VITA_PRICE_LISTVAT_26.08.xlsx</t>
+          <t>classic_WATI_FOR_SKIN_PRICE_LISTVAT_26.07.xlsx</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3802,7 +3932,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3816,7 +3946,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3833,7 +3963,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>classic_DEAR_KLAIRS_PRICE_LISTVAT_26.08.xlsx</t>
+          <t>classic_ARENCIA_PRICE_LIST_VAT_26.08.xlsx</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3862,7 +3992,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3879,7 +4009,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>classic_DR.JART_PRICE_LIST_2026.08VAT.xlsx</t>
+          <t>classic_DAENG_GI_MEO_RI_PRICE_LISTVAT_26.08.xlsx</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3908,7 +4038,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3925,7 +4055,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>classic_DR.PEPTI_PRICE_LISTVAT_26.08.xlsx</t>
+          <t>classic_DAYCELLDr.VITA_PRICE_LISTVAT_26.08.xlsx</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3954,7 +4084,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3971,7 +4101,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>classic_FLORODORA_PRICE_LIST_26.08.xlsx</t>
+          <t>classic_DEAR_KLAIRS_PRICE_LISTVAT_26.08.xlsx</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4000,7 +4130,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -4017,7 +4147,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>classic_FORTHESKIN_PRICE_LISTVAT_26.08.xlsx</t>
+          <t>classic_DR.JART_PRICE_LIST_2026.08VAT.xlsx</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4046,7 +4176,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -4063,7 +4193,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>classic_ISNTREE_Price_listVAT_26.08.xlsx</t>
+          <t>classic_DR.PEPTI_PRICE_LISTVAT_26.08.xlsx</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4092,7 +4222,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -4109,7 +4239,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>classic_LANEIGE_PRICE_LISTVAT_26.08.xlsx</t>
+          <t>classic_FLORODORA_PRICE_LIST_26.08.xlsx</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4138,7 +4268,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4155,7 +4285,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>classic_ROUNDLAB_PRICE_LIST_26.08VAT.xlsx</t>
+          <t>classic_FORTHESKIN_PRICE_LISTVAT_26.08.xlsx</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4184,7 +4314,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -4201,7 +4331,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>classic_SUJI_KOREA_ANJO_PRICE_LIST_2026.08_VAT.xlsx</t>
+          <t>classic_ISNTREE_Price_listVAT_26.08.xlsx</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4230,7 +4360,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>192</v>
+        <v>61</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -4247,7 +4377,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>classic_BERGAMO_PRICE_LIST_26.09VAT.xlsx</t>
+          <t>classic_LANEIGE_PRICE_LISTVAT_26.08.xlsx</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4262,7 +4392,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4276,7 +4406,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -4293,7 +4423,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>classic_ELIZAVECCA_PRICE_LISTVAT_26.09S.xlsx</t>
+          <t>classic_ROUNDLAB_PRICE_LIST_26.08VAT.xlsx</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4308,7 +4438,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4322,7 +4452,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4339,12 +4469,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DERMAFACTORY_26.01.xlsx</t>
+          <t>classic_SUJI_KOREA_ANJO_PRICE_LIST_2026.08_VAT.xlsx</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KR_dermafactory</t>
+          <t>KR_classic</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4354,7 +4484,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4368,7 +4498,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>85</v>
+        <v>192</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -4385,12 +4515,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DR_ALTHEA_PRICE_LIST_VAT_26.02.xlsx</t>
+          <t>classic_BERGAMO_PRICE_LIST_26.09VAT.xlsx</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>KR_dralthea</t>
+          <t>KR_classic</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4400,7 +4530,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4414,7 +4544,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4431,12 +4561,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ge_global_Im_Sorry_for_My_Skin_2607.xlsx</t>
+          <t>classic_ELIZAVECCA_PRICE_LISTVAT_26.09S.xlsx</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KR_ge_global</t>
+          <t>KR_classic</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4446,7 +4576,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4460,7 +4590,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -4477,12 +4607,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ge_global_Jigott_2607.xlsx</t>
+          <t>DERMAFACTORY_26.01.xlsx</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>KR_ge_global</t>
+          <t>KR_dermafactory</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4492,7 +4622,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4506,7 +4636,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>213</v>
+        <v>85</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -4523,12 +4653,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ge_global_SO.NATURAL_2607.xlsx</t>
+          <t>DR_ALTHEA_PRICE_LIST_VAT_26.02.xlsx</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>KR_ge_global</t>
+          <t>KR_dralthea</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4538,7 +4668,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4552,7 +4682,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -4569,7 +4699,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ge_global_VT_2607.xlsx</t>
+          <t>ge_global_Im_Sorry_for_My_Skin_2607.xlsx</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4598,7 +4728,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>140</v>
+        <v>29</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4615,7 +4745,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ge_global_COSDEBAHA_2608.xlsx</t>
+          <t>ge_global_Jigott_2607.xlsx</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4630,7 +4760,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4644,7 +4774,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>65</v>
+        <v>213</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -4661,7 +4791,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ge_global_ETUDE_2608.xlsx</t>
+          <t>ge_global_SO.NATURAL_2607.xlsx</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4676,7 +4806,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4690,7 +4820,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>413</v>
+        <v>45</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -4707,7 +4837,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ge_global_Hetras_2608.xlsx</t>
+          <t>ge_global_VT_2607.xlsx</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4722,7 +4852,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4736,7 +4866,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -4753,7 +4883,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ge_global_Medipeel_2608.xlsx</t>
+          <t>ge_global_COSDEBAHA_2608.xlsx</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4782,7 +4912,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>215</v>
+        <v>65</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -4799,7 +4929,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ge_global_ROUNDLAB_2608.xlsx</t>
+          <t>ge_global_ETUDE_2608.xlsx</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4828,7 +4958,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>114</v>
+        <v>413</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -4845,7 +4975,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ge_global_celimax_2608.xlsx</t>
+          <t>ge_global_Hetras_2608.xlsx</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4874,7 +5004,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -4891,7 +5021,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ge_global_AMORE_2609.xls</t>
+          <t>ge_global_Medipeel_2608.xlsx</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4906,7 +5036,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4916,11 +5046,11 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>xls</t>
+          <t>xlsx</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -4937,12 +5067,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>glowbeauty_Celimax_Pricelist_2026.xlsx</t>
+          <t>ge_global_ROUNDLAB_2608.xlsx</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>KR_glowbeauty</t>
+          <t>KR_ge_global</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4952,7 +5082,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4966,7 +5096,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -4978,21 +5108,17 @@
           <t>разбор скриптом</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>дата прайса: только год</t>
-        </is>
-      </c>
+      <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>glowbeauty_Etude_Pricelist_2026.xlsx</t>
+          <t>ge_global_celimax_2608.xlsx</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>KR_glowbeauty</t>
+          <t>KR_ge_global</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5002,7 +5128,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5016,7 +5142,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>482</v>
+        <v>74</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -5028,21 +5154,17 @@
           <t>разбор скриптом</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>дата прайса: только год</t>
-        </is>
-      </c>
+      <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>glowbeauty_Manyo_Pricelist_2026.xlsx</t>
+          <t>ge_global_AMORE_2609.xls</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KR_glowbeauty</t>
+          <t>KR_ge_global</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5052,7 +5174,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5062,11 +5184,11 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>xls</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>46</v>
+        <v>239</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -5078,16 +5200,12 @@
           <t>разбор скриптом</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>дата прайса: только год</t>
-        </is>
-      </c>
+      <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>glowbeauty_Medicube_Pricelist_2026.xlsx</t>
+          <t>glowbeauty_Celimax_Pricelist_2026.xlsx</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5116,7 +5234,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>182</v>
+        <v>74</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -5137,7 +5255,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>glowbeauty_Medipeel_Pricelist_2026.xlsx</t>
+          <t>glowbeauty_Etude_Pricelist_2026.xlsx</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5166,7 +5284,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>188</v>
+        <v>482</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -5187,7 +5305,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>glowbeauty_Round_Lab_Pricelist_2026.xlsx</t>
+          <t>glowbeauty_Manyo_Pricelist_2026.xlsx</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5216,7 +5334,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -5237,7 +5355,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>glowbeauty_VT_cosmetics_pricelist_2026.xlsx</t>
+          <t>glowbeauty_Medicube_Pricelist_2026.xlsx</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5266,7 +5384,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -5287,12 +5405,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HolikaHolika_PRICE_LIST_VAT_2025.05.xlsx</t>
+          <t>glowbeauty_Medipeel_Pricelist_2026.xlsx</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>KR_holikaholika</t>
+          <t>KR_glowbeauty</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5302,7 +5420,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5316,7 +5434,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>522</v>
+        <v>188</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -5328,17 +5446,21 @@
           <t>разбор скриптом</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>дата прайса: только год</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MASIL_PRICE_LIST_VAT_26.04.xlsx</t>
+          <t>glowbeauty_Round_Lab_Pricelist_2026.xlsx</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>KR_masil</t>
+          <t>KR_glowbeauty</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5348,7 +5470,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5362,7 +5484,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -5374,17 +5496,21 @@
           <t>разбор скриптом</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>дата прайса: только год</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ROUNDLAB_PRICE_LIST_25.11.xlsx</t>
+          <t>glowbeauty_VT_cosmetics_pricelist_2026.xlsx</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>KR_roundlab</t>
+          <t>KR_glowbeauty</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5394,7 +5520,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5408,7 +5534,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>100</v>
+        <v>187</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -5420,17 +5546,21 @@
           <t>разбор скриптом</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>дата прайса: только год</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SKIN1004_PRICE_LIST_26.05.xlsx</t>
+          <t>HolikaHolika_PRICE_LIST_VAT_2025.05.xlsx</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>KR_skin1004</t>
+          <t>KR_holikaholika</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5440,7 +5570,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5454,7 +5584,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>141</v>
+        <v>522</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -5471,48 +5601,278 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>MASIL_PRICE_LIST_VAT_26.04.xlsx</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>KR_masil</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>93</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>разбор скриптом</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>papacosmetic_26.07.01_PAPACOSMETIC_MAANYO_LIST0.xlsx</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>KR_papacosmetic</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>44</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>разбор скриптом</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>papacosmetic_26.08.26_PAPACOSMETIC_CELIMAX_LIST0.xlsx</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>KR_papacosmetic</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>54</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>разбор скриптом</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ROUNDLAB_PRICE_LIST_25.11.xlsx</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>KR_roundlab</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>100</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>разбор скриптом</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>SKIN1004_PRICE_LIST_26.05.xlsx</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>KR_skin1004</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>141</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>разбор скриптом</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>VT_PRICE_LIST_VAT_25.05.xlsx</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>KR_vt</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>xlsx</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
         <v>189</v>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>разбор скриптом</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>разбор скриптом</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5525,7 +5885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5572,57 +5932,57 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>G&amp;E Global, GlowBeauty, Классик</t>
+          <t>G&amp;E Global, GlowBeauty, Аннеси, Классик</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>Аннеси</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>142</v>
+        <v>89</v>
       </c>
       <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ROUNDLAB</t>
+          <t>CELIMAX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>G&amp;E Global, Классик, Прямой прайс бренда</t>
+          <t>G&amp;E Global, GlowBeauty, Аннеси, Прямой прайс бренда</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>Прямой прайс бренда</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CELIMAX</t>
+          <t>ROUNDLAB</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5630,19 +5990,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>G&amp;E Global, GlowBeauty, Прямой прайс бренда</t>
+          <t>G&amp;E Global, Классик, Прямой прайс бренда</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Прямой прайс бренда</t>
+          <t>G&amp;E Global</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="G4" t="inlineStr"/>
     </row>
@@ -5784,7 +6144,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3W CLINIC</t>
+          <t>26.07.01 PAPACOSMETIC MAANYO LIST0</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5792,7 +6152,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>Papa Cosmetic</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -5815,7 +6175,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3W CLINIC LAB</t>
+          <t>26.08.26 PAPACOSMETIC CELIMAX LIST0</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5823,7 +6183,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>Papa Cosmetic</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -5846,7 +6206,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3W CLINIC PREMIUM</t>
+          <t>3W CLINIC</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5877,7 +6237,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ABIB</t>
+          <t>3W CLINIC LAB</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5908,7 +6268,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALFREDO FEEMAS</t>
+          <t>3W CLINIC PREMIUM</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5939,7 +6299,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALFREDO FEEMAS (알프레드 휘마스)</t>
+          <t>ABIB</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5970,7 +6330,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AMORE</t>
+          <t>ALFREDO FEEMAS</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5978,7 +6338,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -6001,7 +6361,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMORE PACIFIC</t>
+          <t>ALFREDO FEEMAS (알프레드 휘마스)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -6032,7 +6392,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ANOTHERFACE</t>
+          <t>AMORE</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -6040,7 +6400,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>G&amp;E Global</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -6063,7 +6423,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ANUA</t>
+          <t>AMORE PACIFIC</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -6071,7 +6431,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Прямой прайс бренда</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -6094,7 +6454,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>APIEU</t>
+          <t>ANOTHERFACE</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -6125,7 +6485,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ARENCIA</t>
+          <t>ANUA</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6133,7 +6493,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>Прямой прайс бренда</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -6156,7 +6516,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AXISY</t>
+          <t>APIEU</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -6164,7 +6524,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Прямой прайс бренда</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -6187,7 +6547,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BEAUTY OF JOSEON</t>
+          <t>ARENCIA</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -6218,7 +6578,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BEPLAIN</t>
+          <t>AXISY</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -6226,7 +6586,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>Прямой прайс бренда</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -6249,7 +6609,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BERGAMO</t>
+          <t>BEAUTY OF JOSEON</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -6280,7 +6640,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BIODANCE</t>
+          <t>BEPLAIN</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -6311,7 +6671,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BY WISHTREND</t>
+          <t>BERGAMO</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -6342,7 +6702,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C2Y</t>
+          <t>BIODANCE</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -6373,7 +6733,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CENTELLIAN 24 MADECA</t>
+          <t>BY WISHTREND</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -6404,7 +6764,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CHARDE</t>
+          <t>C2Y</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -6435,7 +6795,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CHOGONGJIN</t>
+          <t>CENTELLIAN 24 MADECA</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -6466,7 +6826,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>COSDEBAHA</t>
+          <t>CHARDE</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -6474,7 +6834,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -6497,7 +6857,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CP1</t>
+          <t>CHOGONGJIN</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -6528,7 +6888,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DAENG GI MEO RI</t>
+          <t>COSDEBAHA</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -6536,7 +6896,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>G&amp;E Global</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -6559,7 +6919,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DASIQUE</t>
+          <t>CP1</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -6590,7 +6950,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DAYCELLDR.VITA</t>
+          <t>DAENG GI MEO RI</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -6621,7 +6981,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DEAR KLAIRS</t>
+          <t>DASIQUE</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -6652,7 +7012,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DERMAFACTORY</t>
+          <t>DAYCELLDR.VITA</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -6660,7 +7020,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Прямой прайс бренда</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -6683,7 +7043,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DR ALTHEA</t>
+          <t>DEAR KLAIRS</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -6691,7 +7051,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Прямой прайс бренда</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -6714,7 +7074,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DR. ALTHEA</t>
+          <t>DERMAFACTORY</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -6722,7 +7082,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>Прямой прайс бренда</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -6745,7 +7105,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DR.JART</t>
+          <t>DR ALTHEA</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -6753,7 +7113,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>Прямой прайс бренда</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -6776,7 +7136,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DR.PEPTI</t>
+          <t>DR. ALTHEA</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -6807,7 +7167,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EIOM</t>
+          <t>DR.JART</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -6838,7 +7198,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EKEL</t>
+          <t>DR.PEPTI</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -6869,7 +7229,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ELIZAVECCA</t>
+          <t>EIOM</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -6900,7 +7260,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ESHUMI</t>
+          <t>EKEL</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -6931,7 +7291,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EVAS</t>
+          <t>ELIZAVECCA</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -6962,7 +7322,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FLOR DE MAN</t>
+          <t>ESHUMI</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -6993,7 +7353,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FLORODORA</t>
+          <t>EVAS</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -7024,7 +7384,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FORTHESKIN</t>
+          <t>FLOR DE MAN</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -7055,7 +7415,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HEIMISH</t>
+          <t>FLORODORA</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -7086,7 +7446,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HETRAS</t>
+          <t>FORTHESKIN</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -7094,7 +7454,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -7117,7 +7477,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HOLIKAHOLIKA</t>
+          <t>HEIMISH</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -7125,7 +7485,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Прямой прайс бренда</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -7148,7 +7508,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Happy Bath</t>
+          <t>HETRAS</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -7156,7 +7516,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>G&amp;E Global</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -7179,7 +7539,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>IM FROM</t>
+          <t>HOLIKAHOLIKA</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -7187,7 +7547,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>Прямой прайс бренда</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -7210,7 +7570,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ISNTREE</t>
+          <t>Happy Bath</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -7241,7 +7601,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JUMISO</t>
+          <t>IM FROM</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -7272,7 +7632,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LAGOM</t>
+          <t>ISNTREE</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -7303,7 +7663,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LANEIGE</t>
+          <t>JUMISO</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -7334,7 +7694,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LEBELAGE</t>
+          <t>LAGOM</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -7365,7 +7725,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LUNARIS</t>
+          <t>LAMELIN</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -7373,7 +7733,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>Аннеси</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -7396,7 +7756,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LUNARIS (루나리스)</t>
+          <t>LANEIGE</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -7427,7 +7787,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MASIL</t>
+          <t>LEBELAGE</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -7435,7 +7795,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Прямой прайс бренда</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -7458,7 +7818,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MEDICUBE</t>
+          <t>LUNARIS</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -7466,7 +7826,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GlowBeauty</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -7489,7 +7849,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MELASMAX</t>
+          <t>LUNARIS (루나리스)</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -7520,7 +7880,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MISSHA</t>
+          <t>MASIL</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -7528,7 +7888,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>Прямой прайс бренда</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -7551,7 +7911,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Median</t>
+          <t>MEDICUBE</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -7559,7 +7919,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>GlowBeauty</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -7582,7 +7942,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>NAEXY</t>
+          <t>MELASMAX</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -7613,7 +7973,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NEOPHARM</t>
+          <t>MISSHA</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -7644,7 +8004,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NINELESS</t>
+          <t>Median</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -7675,7 +8035,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>NAEXY</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -7706,7 +8066,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PRORANCE</t>
+          <t>NEOPHARM</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -7737,7 +8097,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PYUNKANG YUL</t>
+          <t>NINELESS</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -7768,7 +8128,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>RATAPLAN</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -7799,7 +8159,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>PRORANCE</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -7807,7 +8167,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GlowBeauty</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -7830,7 +8190,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SANSUYOU</t>
+          <t>PYUNKANG YUL</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -7861,7 +8221,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SANSUYOU (산수유)</t>
+          <t>RATAPLAN</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -7892,7 +8252,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SKIN APPLE</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -7900,7 +8260,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>GlowBeauty</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -7923,7 +8283,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SKIN1004</t>
+          <t>SANSUYOU</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -7931,7 +8291,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Прямой прайс бренда</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -7954,7 +8314,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SO.NATURAL</t>
+          <t>SANSUYOU (산수유)</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -7962,7 +8322,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -7985,7 +8345,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SOME BY MI</t>
+          <t>SKIN APPLE</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -8016,7 +8376,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STARLIKE</t>
+          <t>SKIN1004</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -8024,7 +8384,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>Прямой прайс бренда</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -8047,7 +8407,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SUJI KOREA ANJO</t>
+          <t>SO.NATURAL</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -8055,7 +8415,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>G&amp;E Global</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -8078,7 +8438,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TENZERO</t>
+          <t>SOME BY MI</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -8109,7 +8469,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VT COSMETICS</t>
+          <t>STARLIKE</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -8117,7 +8477,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GlowBeauty</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -8140,7 +8500,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>WATI FOR SKIN</t>
+          <t>SUJI KOREA ANJO</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -8171,7 +8531,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>WELCOS</t>
+          <t>TENZERO</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -8202,7 +8562,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>려</t>
+          <t>VT COSMETICS</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -8210,7 +8570,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>GlowBeauty</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -8233,7 +8593,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>메디안</t>
+          <t>WATI FOR SKIN</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -8264,7 +8624,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>미쟝센</t>
+          <t>WELCOS</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -8295,29 +8655,122 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>려</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>выбора нет, поставщик один</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>메디안</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>выбора нет, поставщик один</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>미쟝센</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Классик</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>выбора нет, поставщик один</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>스킨유</t>
         </is>
       </c>
-      <c r="B91" t="n">
-        <v>1</v>
-      </c>
-      <c r="C91" t="inlineStr">
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="inlineStr">
         <is>
           <t>Классик</t>
         </is>
       </c>
-      <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="inlineStr">
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="inlineStr">
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>выбора нет, поставщик один</t>
         </is>

--- a/outputs/supplier_passport.xlsx
+++ b/outputs/supplier_passport.xlsx
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="M2" t="n">
         <v>5932</v>
@@ -711,7 +711,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KR_holikaholika</t>
+          <t>KR_papacosmetic</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -726,63 +726,63 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HOLIKAHOLIKA</t>
+          <t>Papacosmetic Co., Ltd</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>бренд</t>
+          <t>экспортер</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>г. Кимпхо</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>EXW</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>EXW</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M5" t="n">
-        <v>522</v>
+        <v>666</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>прямой прайс бренда; позиций: 522</t>
+          <t>минимальный заказ 100 000 000 KRW; оплата 50% + 50%; прайс CELIMAX содержит два листа с одинаковым набором товаров и ценами, отличающимися на 2.5% — взят более дорогой лист</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KR_annecy</t>
+          <t>KR_holikaholika</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -797,17 +797,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Аннеси (Annecy)</t>
+          <t>HOLIKAHOLIKA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>посредник</t>
+          <t>бренд</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>annecy.kr</t>
+          <t>уточнить</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>указано не во всех прайсах: 10000000 KRW (прайсов: 1)</t>
+          <t>уточнить</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -836,24 +836,24 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>430</v>
+        <v>522</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>по CELIMAX в шапке прайса указано, что запрещенных к экспорту стран нет; у LAMELIN две цены по объему заказа — уточнить пороги</t>
+          <t>прямой прайс бренда; позиций: 522</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KR_vt</t>
+          <t>KR_annecy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -868,63 +868,63 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>Аннеси (Annecy)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>бренд</t>
+          <t>посредник</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>annecy.kr</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EXW</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>указано не во всех прайсах: 10000000 KRW (прайсов: 1)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EXW</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>189</v>
+        <v>430</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>прямой прайс бренда; позиций: 189</t>
+          <t>по CELIMAX в шапке прайса указано, что запрещенных к экспорту стран нет; у LAMELIN две цены по объему заказа — уточнить пороги</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KR_skin1004</t>
+          <t>KR_vt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SKIN1004</t>
+          <t>VT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -981,21 +981,21 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>прямой прайс бренда; позиций: 141</t>
+          <t>прямой прайс бренда; позиций: 189</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KR_roundlab</t>
+          <t>KR_skin1004</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ROUNDLAB</t>
+          <t>SKIN1004</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1052,21 +1052,21 @@
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>прямой прайс бренда; позиций: 100</t>
+          <t>прямой прайс бренда; позиций: 141</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KR_papacosmetic</t>
+          <t>KR_roundlab</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Papacosmetic Co., Ltd</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>экспортер</t>
+          <t>бренд</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>г. Кимпхо</t>
+          <t>уточнить</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1120,17 +1120,17 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>минимальный заказ 100 000 000 KRW; оплата 50% + 50%; прайс CELIMAX содержит два листа с одинаковым набором товаров и ценами, отличающимися на 2.5% — взят более дорогой лист</t>
+          <t>прямой прайс бренда; позиций: 100</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DR ALTHEA</t>
+          <t>DR. ALTHEA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1571,7 +1571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5647,7 +5647,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>papacosmetic_26.07.01_PAPACOSMETIC_MAANYO_LIST0.xlsx</t>
+          <t>papacosmetic_26.07.01_PAPACOSMETIC_ANUA_LIST0.xlsx</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>papacosmetic_26.08.26_PAPACOSMETIC_CELIMAX_LIST0.xlsx</t>
+          <t>papacosmetic_26.07.01_PAPACOSMETIC_CELIMAX_LIST0.xlsx</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5739,12 +5739,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ROUNDLAB_PRICE_LIST_25.11.xlsx</t>
+          <t>papacosmetic_26.07.01_PAPACOSMETIC_DERMAFACTORY_LIST0.xlsx</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>KR_roundlab</t>
+          <t>KR_papacosmetic</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5768,7 +5768,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -5785,12 +5785,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SKIN1004_PRICE_LIST_26.05.xlsx</t>
+          <t>papacosmetic_26.07.01_PAPACOSMETIC_MAANYO_LIST0.xlsx</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>KR_skin1004</t>
+          <t>KR_papacosmetic</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5814,7 +5814,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -5831,48 +5831,324 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>papacosmetic_26.07.01_PAPACOSMETIC_MEDICUBE_LIST0.xlsx</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>KR_papacosmetic</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>129</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>разбор скриптом</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>papacosmetic_26.07.01_PAPACOSMETIC_ROUNDLAB_LIST0.xlsx</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>KR_papacosmetic</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>114</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>разбор скриптом</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>papacosmetic_26.07.01_PAPACOSMETIC_SKIN1004_LIST0.xlsx</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>KR_papacosmetic</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>95</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>разбор скриптом</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>papacosmetic_26.08.26_PAPACOSMETIC_CELIMAX_LIST0.xlsx</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>KR_papacosmetic</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>54</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>разбор скриптом</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ROUNDLAB_PRICE_LIST_25.11.xlsx</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>KR_roundlab</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>100</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>разбор скриптом</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>SKIN1004_PRICE_LIST_26.05.xlsx</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>KR_skin1004</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>141</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>разбор скриптом</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
           <t>VT_PRICE_LIST_VAT_25.05.xlsx</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>KR_vt</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>xlsx</t>
-        </is>
-      </c>
-      <c r="G93" t="n">
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
         <v>189</v>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>разбор скриптом</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>разбор скриптом</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5885,7 +6161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5928,27 +6204,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MEDIPEEL</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>G&amp;E Global, GlowBeauty, Аннеси, Классик</t>
+          <t>G&amp;E Global, GlowBeauty, Papa Cosmetic, Классик, Прямой прайс бренда</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>193</v>
+        <v>117</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Аннеси</t>
+          <t>G&amp;E Global</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="G2" t="inlineStr"/>
     </row>
@@ -5959,11 +6235,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>G&amp;E Global, GlowBeauty, Аннеси, Прямой прайс бренда</t>
+          <t>G&amp;E Global, GlowBeauty, Papa Cosmetic, Аннеси, Прямой прайс бренда</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -5975,95 +6251,95 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ROUNDLAB</t>
+          <t>MEDIPEEL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>G&amp;E Global, Классик, Прямой прайс бренда</t>
+          <t>G&amp;E Global, GlowBeauty, Аннеси, Классик</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>113</v>
+        <v>193</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>Аннеси</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>VT</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>G&amp;E Global, Классик</t>
+          <t>G&amp;E Global, GlowBeauty, Прямой прайс бренда</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>Прямой прайс бренда</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>208</v>
+        <v>98</v>
       </c>
       <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>G&amp;E Global, Прямой прайс бренда</t>
+          <t>GlowBeauty, Papa Cosmetic, Классик</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>113</v>
+        <v>44</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Прямой прайс бренда</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6071,11 +6347,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GlowBeauty, Классик</t>
+          <t>G&amp;E Global, Классик</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>44</v>
+        <v>208</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -6083,14 +6359,14 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>44</v>
+        <v>208</v>
       </c>
       <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ETUDE</t>
+          <t>ANUA</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6098,26 +6374,26 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>G&amp;E Global, GlowBeauty</t>
+          <t>Papa Cosmetic, Прямой прайс бренда</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Papa Cosmetic</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IM SORRY FOR MY SKIN</t>
+          <t>DERMAFACTORY</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6125,96 +6401,88 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>G&amp;E Global, Классик</t>
+          <t>Papa Cosmetic, Прямой прайс бренда</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Прямой прайс бренда</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>26.07.01 PAPACOSMETIC MAANYO LIST0</t>
+          <t>MEDICUBE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>GlowBeauty, Papa Cosmetic</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>73</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Papa Cosmetic</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>выбора нет, поставщик один</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>26.08.26 PAPACOSMETIC CELIMAX LIST0</t>
+          <t>DR. ALTHEA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Papa Cosmetic</t>
+          <t>Классик, Прямой прайс бренда</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>выбора нет, поставщик один</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3W CLINIC</t>
+          <t>AMORE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>G&amp;E Global, Классик</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -6228,24 +6496,20 @@
       <c r="F12" t="n">
         <v>0</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>выбора нет, поставщик один</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3W CLINIC LAB</t>
+          <t>ETUDE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>G&amp;E Global, GlowBeauty</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -6259,24 +6523,20 @@
       <c r="F13" t="n">
         <v>0</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>выбора нет, поставщик один</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3W CLINIC PREMIUM</t>
+          <t>IM SORRY FOR MY SKIN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>G&amp;E Global, Классик</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -6290,24 +6550,20 @@
       <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>выбора нет, поставщик один</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ABIB</t>
+          <t>SKIN1004</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>Papa Cosmetic, Прямой прайс бренда</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -6321,16 +6577,12 @@
       <c r="F15" t="n">
         <v>0</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>выбора нет, поставщик один</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALFREDO FEEMAS</t>
+          <t>3W CLINIC</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -6361,7 +6613,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ALFREDO FEEMAS (알프레드 휘마스)</t>
+          <t>ABIB</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -6392,7 +6644,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMORE</t>
+          <t>ALFREDO FEEMAS</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -6400,7 +6652,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -6423,7 +6675,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMORE PACIFIC</t>
+          <t>ANOTHERFACE</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -6454,7 +6706,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ANOTHERFACE</t>
+          <t>APIEU</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -6485,7 +6737,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ANUA</t>
+          <t>ARENCIA</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6493,7 +6745,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Прямой прайс бренда</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -6516,7 +6768,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>APIEU</t>
+          <t>AXISY</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -6524,7 +6776,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>Прямой прайс бренда</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -6547,7 +6799,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ARENCIA</t>
+          <t>BEAUTY OF JOSEON</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -6578,7 +6830,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AXISY</t>
+          <t>BEPLAIN</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -6586,7 +6838,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Прямой прайс бренда</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -6609,7 +6861,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BEAUTY OF JOSEON</t>
+          <t>BERGAMO</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -6640,7 +6892,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BEPLAIN</t>
+          <t>BIODANCE</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -6671,7 +6923,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BERGAMO</t>
+          <t>BY WISHTREND</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -6702,7 +6954,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BIODANCE</t>
+          <t>C2Y</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -6733,7 +6985,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BY WISHTREND</t>
+          <t>CENTELLIAN 24 MADECA</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -6764,7 +7016,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C2Y</t>
+          <t>CHARDE</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -6795,7 +7047,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CENTELLIAN 24 MADECA</t>
+          <t>CHOGONGJIN</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -6826,7 +7078,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CHARDE</t>
+          <t>COSDEBAHA</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -6834,7 +7086,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>G&amp;E Global</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -6857,7 +7109,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CHOGONGJIN</t>
+          <t>CP1</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -6888,7 +7140,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>COSDEBAHA</t>
+          <t>DAENG GI MEO RI</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -6896,7 +7148,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -6919,7 +7171,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CP1</t>
+          <t>DASIQUE</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -6950,7 +7202,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DAENG GI MEO RI</t>
+          <t>DAYCELLDR.VITA</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -6981,7 +7233,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DASIQUE</t>
+          <t>DEAR KLAIRS</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -7012,7 +7264,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DAYCELLDR.VITA</t>
+          <t>DR.JART</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -7043,7 +7295,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DEAR KLAIRS</t>
+          <t>DR.PEPTI</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -7074,7 +7326,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DERMAFACTORY</t>
+          <t>EIOM</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -7082,7 +7334,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Прямой прайс бренда</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -7105,7 +7357,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DR ALTHEA</t>
+          <t>EKEL</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -7113,7 +7365,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Прямой прайс бренда</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -7136,7 +7388,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DR. ALTHEA</t>
+          <t>ELIZAVECCA</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -7167,7 +7419,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DR.JART</t>
+          <t>ESHUMI</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -7198,7 +7450,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DR.PEPTI</t>
+          <t>EVAS</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -7229,7 +7481,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EIOM</t>
+          <t>FLOR DE MAN</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -7260,7 +7512,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EKEL</t>
+          <t>FLORODORA</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -7291,7 +7543,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ELIZAVECCA</t>
+          <t>FORTHESKIN</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -7322,7 +7574,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ESHUMI</t>
+          <t>HEIMISH</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -7353,7 +7605,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EVAS</t>
+          <t>HETRAS</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -7361,7 +7613,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>G&amp;E Global</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -7384,7 +7636,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FLOR DE MAN</t>
+          <t>HOLIKAHOLIKA</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -7392,7 +7644,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>Прямой прайс бренда</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -7415,7 +7667,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FLORODORA</t>
+          <t>Happy Bath</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -7446,7 +7698,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FORTHESKIN</t>
+          <t>IM FROM</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -7477,7 +7729,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HEIMISH</t>
+          <t>ISNTREE</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -7508,7 +7760,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>HETRAS</t>
+          <t>JUMISO</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -7516,7 +7768,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -7539,7 +7791,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HOLIKAHOLIKA</t>
+          <t>LAGOM</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -7547,7 +7799,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Прямой прайс бренда</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -7570,7 +7822,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Happy Bath</t>
+          <t>LAMELIN</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -7578,7 +7830,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>Аннеси</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -7601,7 +7853,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IM FROM</t>
+          <t>LANEIGE</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -7632,7 +7884,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ISNTREE</t>
+          <t>LEBELAGE</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -7663,7 +7915,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>JUMISO</t>
+          <t>LUNARIS</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -7694,7 +7946,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LAGOM</t>
+          <t>MASIL</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -7702,7 +7954,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>Прямой прайс бренда</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -7725,7 +7977,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LAMELIN</t>
+          <t>MELASMAX</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -7733,7 +7985,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Аннеси</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -7756,7 +8008,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LANEIGE</t>
+          <t>MISSHA</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -7787,7 +8039,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LEBELAGE</t>
+          <t>Median</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -7818,7 +8070,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LUNARIS</t>
+          <t>NAEXY</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -7849,7 +8101,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LUNARIS (루나리스)</t>
+          <t>NEOPHARM</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -7880,7 +8132,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MASIL</t>
+          <t>NINELESS</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -7888,7 +8140,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Прямой прайс бренда</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -7911,7 +8163,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MEDICUBE</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -7919,7 +8171,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GlowBeauty</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -7942,7 +8194,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MELASMAX</t>
+          <t>PRORANCE</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -7973,7 +8225,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MISSHA</t>
+          <t>PYUNKANG YUL</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -8004,7 +8256,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Median</t>
+          <t>RATAPLAN</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -8035,7 +8287,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NAEXY</t>
+          <t>SANSUYOU</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -8066,7 +8318,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NEOPHARM</t>
+          <t>SKIN APPLE</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -8097,7 +8349,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NINELESS</t>
+          <t>SO.NATURAL</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -8105,7 +8357,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Классик</t>
+          <t>G&amp;E Global</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -8128,7 +8380,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>SOME BY MI</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -8159,7 +8411,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PRORANCE</t>
+          <t>STARLIKE</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -8190,7 +8442,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PYUNKANG YUL</t>
+          <t>SUJI KOREA ANJO</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -8221,7 +8473,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RATAPLAN</t>
+          <t>TENZERO</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -8252,7 +8504,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>WATI FOR SKIN</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -8260,7 +8512,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GlowBeauty</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -8283,7 +8535,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SANSUYOU</t>
+          <t>WELCOS</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -8314,7 +8566,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SANSUYOU (산수유)</t>
+          <t>려</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -8345,7 +8597,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SKIN APPLE</t>
+          <t>메디안</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -8376,7 +8628,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SKIN1004</t>
+          <t>미쟝센</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -8384,7 +8636,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Прямой прайс бренда</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -8407,7 +8659,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SO.NATURAL</t>
+          <t>스킨유</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -8415,7 +8667,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>G&amp;E Global</t>
+          <t>Классик</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -8430,347 +8682,6 @@
         <v>0</v>
       </c>
       <c r="G83" t="inlineStr">
-        <is>
-          <t>выбора нет, поставщик один</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>SOME BY MI</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>1</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>выбора нет, поставщик один</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>STARLIKE</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>выбора нет, поставщик один</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>SUJI KOREA ANJO</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>выбора нет, поставщик один</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>TENZERO</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>1</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>выбора нет, поставщик один</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>VT COSMETICS</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>1</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>GlowBeauty</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>выбора нет, поставщик один</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>WATI FOR SKIN</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>1</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>выбора нет, поставщик один</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>WELCOS</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>1</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>выбора нет, поставщик один</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>려</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>1</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>выбора нет, поставщик один</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>메디안</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>1</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>выбора нет, поставщик один</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>미쟝센</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>1</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>выбора нет, поставщик один</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>스킨유</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>1</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" t="inlineStr">
         <is>
           <t>выбора нет, поставщик один</t>
         </is>
